--- a/survey_templates/035_store_features_evaluation_form--survey_templates.xlsx
+++ b/survey_templates/035_store_features_evaluation_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>store_features_form</t>
+          <t>store_hours</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Store Features Evaluation Form</t>
+          <t>Store Hours</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>store_features_questions</t>
+          <t>store_location</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How would you rate the features of the store?</t>
+          <t>Store Location</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>store_feature_1</t>
+          <t>store_ambiance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Store Hours</t>
+          <t>Store Ambiance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>store_feature_2</t>
+          <t>store_product</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Store Location</t>
+          <t>Store Product</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>store_feature_3</t>
+          <t>store_service</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Store Ambiance</t>
+          <t>Store Service</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>store_feature_4</t>
+          <t>store_price</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Store Product</t>
+          <t>Store Price</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>store_feature_5</t>
+          <t>store_cleanliness</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Store Service</t>
+          <t>Store Cleanliness</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>store_feature_6</t>
+          <t>store_layout</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Store Price</t>
+          <t>Store Layout</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>store_feature_7</t>
+          <t>store_parking</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Store Cleanliness</t>
+          <t>Store Parking</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,366 +722,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>store_feature_8</t>
+          <t>store_security</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Store Layout</t>
+          <t>Store Security</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>store_feature_9</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Store Parking</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>store_feature_10</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Store Security</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>store_feature_11</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Store Safety</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>store_feature_12</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Store Features Evaluation Form</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>store_feature_13</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Store Features Evaluation Form</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>store_feature_14</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Store Features Evaluation Form</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>store_feature_15</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Store Features Evaluation Form</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>store_feature_16</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Store Features Evaluation Form</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>store_feature_17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Store Features Evaluation Form</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>store_feature_18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Store Features Evaluation Form</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>store_feature_19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Store Features Evaluation Form</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>store_feature_20</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Store Features Evaluation Form</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>store_feature_21</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Store Features Evaluation Form</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>store_feature_22</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Store Features Evaluation Form</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>store_feature_23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Store Features Evaluation Form</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +753,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +781,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>store_features_questions_choices</t>
+          <t>store_hours_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +798,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>store_features_questions_choices</t>
+          <t>store_hours_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +815,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>store_features_questions_choices</t>
+          <t>store_hours_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +832,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>store_features_questions_choices</t>
+          <t>store_hours_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,119 +849,255 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>store_feature_6_choices</t>
+          <t>store_service_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>store_feature_6_choices</t>
+          <t>store_service_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>store_feature_6_choices</t>
+          <t>store_service_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>store_feature_7_choices</t>
+          <t>store_service_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>very_clean</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Very Clean</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>store_feature_7_choices</t>
+          <t>store_price_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>somewhat_clean</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Somewhat Clean</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>store_feature_7_choices</t>
+          <t>store_price_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>somewhat_dirty</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Somewhat Dirty</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>store_feature_7_choices</t>
+          <t>store_price_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>store_cleanliness_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>very_clean</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Very Clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>store_cleanliness_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>somewhat_clean</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Somewhat Clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>store_cleanliness_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>somewhat_dirty</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Somewhat Dirty</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>store_cleanliness_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>extremely_dirty</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Extremely Dirty</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>store_security_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>store_security_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>store_security_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>store_security_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
